--- a/corrupt_repaired.xlsx
+++ b/corrupt_repaired.xlsx
@@ -8184,7 +8184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -8620,9 +8620,10 @@
         <f>AG6*AE6</f>
         <v/>
       </c>
-      <c r="AK6" s="6">
-        <f>VLOOKUP(B6,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK6" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="117" customHeight="1">
@@ -8701,9 +8702,10 @@
         <f>AG7*AE7</f>
         <v/>
       </c>
-      <c r="AK7" s="6">
-        <f>VLOOKUP(B7,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK7" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="117" customHeight="1">
@@ -8784,9 +8786,10 @@
         <f>AG8*AE8</f>
         <v/>
       </c>
-      <c r="AK8" s="6">
-        <f>VLOOKUP(B8,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK8" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="117" customHeight="1">
@@ -8865,9 +8868,10 @@
         <f>AG9*AE9</f>
         <v/>
       </c>
-      <c r="AK9" s="6">
-        <f>VLOOKUP(B9,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK9" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="117" customHeight="1">
@@ -8944,9 +8948,10 @@
         <f>AG10*AE10</f>
         <v/>
       </c>
-      <c r="AK10" s="6">
-        <f>VLOOKUP(B10,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK10" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="117" customHeight="1">
@@ -9025,9 +9030,10 @@
         <f>AG11*AE11</f>
         <v/>
       </c>
-      <c r="AK11" s="6">
-        <f>VLOOKUP(B11,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK11" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="117" customHeight="1">
@@ -9104,9 +9110,10 @@
         <f>AG12*AE12</f>
         <v/>
       </c>
-      <c r="AK12" s="6">
-        <f>VLOOKUP(B12,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK12" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="117" customHeight="1">
@@ -9181,9 +9188,10 @@
         <f>AG13*AE13</f>
         <v/>
       </c>
-      <c r="AK13" s="6">
-        <f>VLOOKUP(B13,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK13" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="117" customHeight="1">
@@ -9260,9 +9268,10 @@
         <f>AG14*AE14</f>
         <v/>
       </c>
-      <c r="AK14" s="6">
-        <f>VLOOKUP(B14,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK14" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="117" customHeight="1">
@@ -9339,9 +9348,10 @@
         <f>AG15*AE15</f>
         <v/>
       </c>
-      <c r="AK15" s="6">
-        <f>VLOOKUP(B15,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK15" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="117" customHeight="1">
@@ -9418,9 +9428,10 @@
         <f>AG16*AE16</f>
         <v/>
       </c>
-      <c r="AK16" s="6">
-        <f>VLOOKUP(B16,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK16" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="117" customHeight="1">
@@ -9497,9 +9508,10 @@
         <f>AG17*AE17</f>
         <v/>
       </c>
-      <c r="AK17" s="6">
-        <f>VLOOKUP(B17,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK17" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="117" customHeight="1">
@@ -9576,9 +9588,10 @@
         <f>AG18*AE18</f>
         <v/>
       </c>
-      <c r="AK18" s="6">
-        <f>VLOOKUP(B18,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK18" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="117" customHeight="1">
@@ -9655,9 +9668,10 @@
         <f>AG19*AE19</f>
         <v/>
       </c>
-      <c r="AK19" s="6">
-        <f>VLOOKUP(B19,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK19" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="117" customHeight="1">
@@ -9734,9 +9748,10 @@
         <f>AG20*AE20</f>
         <v/>
       </c>
-      <c r="AK20" s="6">
-        <f>VLOOKUP(B20,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK20" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="117" customHeight="1">
@@ -9815,9 +9830,10 @@
         <f>AG21*AE21</f>
         <v/>
       </c>
-      <c r="AK21" s="6">
-        <f>VLOOKUP(B21,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK21" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="117" customHeight="1">
@@ -9894,9 +9910,10 @@
         <f>AG22*AE22</f>
         <v/>
       </c>
-      <c r="AK22" s="6">
-        <f>VLOOKUP(B22,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK22" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="117" customHeight="1">
@@ -9971,9 +9988,10 @@
         <f>AG23*AE23</f>
         <v/>
       </c>
-      <c r="AK23" s="6">
-        <f>VLOOKUP(B23,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK23" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="117" customHeight="1">
@@ -10050,9 +10068,10 @@
         <f>AG24*AE24</f>
         <v/>
       </c>
-      <c r="AK24" s="6">
-        <f>VLOOKUP(B24,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK24" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="117" customHeight="1">
@@ -10127,9 +10146,10 @@
         <f>AG25*AE25</f>
         <v/>
       </c>
-      <c r="AK25" s="6">
-        <f>VLOOKUP(B25,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK25" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="117" customHeight="1">
@@ -10208,9 +10228,10 @@
         <f>AG26*AE26</f>
         <v/>
       </c>
-      <c r="AK26" s="6">
-        <f>VLOOKUP(B26,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK26" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="117" customHeight="1">
@@ -10295,9 +10316,10 @@
         <f>AG27*AE27</f>
         <v/>
       </c>
-      <c r="AK27" s="6">
-        <f>VLOOKUP(B27,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK27" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="117" customHeight="1">
@@ -10372,9 +10394,10 @@
         <f>AG28*AE28</f>
         <v/>
       </c>
-      <c r="AK28" s="6">
-        <f>VLOOKUP(B28,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK28" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="117" customHeight="1">
@@ -10449,9 +10472,10 @@
         <f>AG29*AE29</f>
         <v/>
       </c>
-      <c r="AK29" s="6">
-        <f>VLOOKUP(B29,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK29" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="117" customHeight="1">
@@ -10528,9 +10552,10 @@
         <f>AG30*AE30</f>
         <v/>
       </c>
-      <c r="AK30" s="6">
-        <f>VLOOKUP(B30,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK30" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="117" customHeight="1">
@@ -10603,9 +10628,10 @@
         <f>AG31*AE31</f>
         <v/>
       </c>
-      <c r="AK31" s="6">
-        <f>VLOOKUP(B31,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK31" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="117" customHeight="1">
@@ -10680,9 +10706,10 @@
         <f>AG32*AE32</f>
         <v/>
       </c>
-      <c r="AK32" s="6">
-        <f>VLOOKUP(B32,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK32" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="117" customHeight="1">
@@ -10763,9 +10790,10 @@
         <f>AG33*AE33</f>
         <v/>
       </c>
-      <c r="AK33" s="6">
-        <f>VLOOKUP(B33,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK33" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="117" customHeight="1">
@@ -10842,9 +10870,10 @@
         <f>AG34*AE34</f>
         <v/>
       </c>
-      <c r="AK34" s="6">
-        <f>VLOOKUP(B34,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK34" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="117" customHeight="1">
@@ -10919,9 +10948,10 @@
         <f>AG35*AE35</f>
         <v/>
       </c>
-      <c r="AK35" s="6">
-        <f>VLOOKUP(B35,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK35" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="117" customHeight="1">
@@ -11002,9 +11032,10 @@
         <f>AG36*AE36</f>
         <v/>
       </c>
-      <c r="AK36" s="6">
-        <f>VLOOKUP(B36,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK36" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="117" customHeight="1">
@@ -11083,9 +11114,10 @@
         <f>AG37*AE37</f>
         <v/>
       </c>
-      <c r="AK37" s="6">
-        <f>VLOOKUP(B37,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK37" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="117" customHeight="1">
@@ -11160,9 +11192,10 @@
         <f>AG38*AE38</f>
         <v/>
       </c>
-      <c r="AK38" s="6">
-        <f>VLOOKUP(B38,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK38" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="117" customHeight="1">
@@ -11243,9 +11276,10 @@
         <f>AG39*AE39</f>
         <v/>
       </c>
-      <c r="AK39" s="6">
-        <f>VLOOKUP(B39,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK39" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="117" customHeight="1">
@@ -11326,9 +11360,10 @@
         <f>AG40*AE40</f>
         <v/>
       </c>
-      <c r="AK40" s="6">
-        <f>VLOOKUP(B40,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK40" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="117" customHeight="1">
@@ -11409,9 +11444,10 @@
         <f>AG41*AE41</f>
         <v/>
       </c>
-      <c r="AK41" s="6">
-        <f>VLOOKUP(B41,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK41" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="117" customHeight="1">
@@ -11486,9 +11522,10 @@
         <f>AG42*AE42</f>
         <v/>
       </c>
-      <c r="AK42" s="6">
-        <f>VLOOKUP(B42,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK42" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="117" customHeight="1">
@@ -11569,9 +11606,10 @@
         <f>AG43*AE43</f>
         <v/>
       </c>
-      <c r="AK43" s="6">
-        <f>VLOOKUP(B43,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK43" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="117" customHeight="1">
@@ -11652,9 +11690,10 @@
         <f>AG44*AE44</f>
         <v/>
       </c>
-      <c r="AK44" s="6">
-        <f>VLOOKUP(B44,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK44" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="117" customHeight="1">
@@ -11735,9 +11774,10 @@
         <f>AG45*AE45</f>
         <v/>
       </c>
-      <c r="AK45" s="6">
-        <f>VLOOKUP(B45,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK45" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="117" customHeight="1">
@@ -11812,9 +11852,10 @@
         <f>AG46*AE46</f>
         <v/>
       </c>
-      <c r="AK46" s="6">
-        <f>VLOOKUP(B46,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK46" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="117" customHeight="1">
@@ -11891,9 +11932,10 @@
         <f>AG47*AE47</f>
         <v/>
       </c>
-      <c r="AK47" s="6">
-        <f>VLOOKUP(B47,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK47" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="117" customHeight="1">
@@ -11972,9 +12014,10 @@
         <f>AG48*AE48</f>
         <v/>
       </c>
-      <c r="AK48" s="6">
-        <f>VLOOKUP(B48,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK48" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="117" customHeight="1">
@@ -12055,9 +12098,10 @@
         <f>AG49*AE49</f>
         <v/>
       </c>
-      <c r="AK49" s="6">
-        <f>VLOOKUP(B49,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK49" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="117" customHeight="1">
@@ -12138,9 +12182,10 @@
         <f>AG50*AE50</f>
         <v/>
       </c>
-      <c r="AK50" s="6">
-        <f>VLOOKUP(B50,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK50" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="117" customHeight="1">
@@ -12217,9 +12262,10 @@
         <f>AG51*AE51</f>
         <v/>
       </c>
-      <c r="AK51" s="6">
-        <f>VLOOKUP(B51,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK51" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="117" customHeight="1">
@@ -12298,9 +12344,10 @@
         <f>AG52*AE52</f>
         <v/>
       </c>
-      <c r="AK52" s="6">
-        <f>VLOOKUP(B52,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK52" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="117" customHeight="1">
@@ -12377,9 +12424,10 @@
         <f>AG53*AE53</f>
         <v/>
       </c>
-      <c r="AK53" s="6">
-        <f>VLOOKUP(B53,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK53" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="117" customHeight="1">
@@ -12458,9 +12506,10 @@
         <f>AG54*AE54</f>
         <v/>
       </c>
-      <c r="AK54" s="6">
-        <f>VLOOKUP(B54,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK54" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="117" customHeight="1">
@@ -12539,9 +12588,10 @@
         <f>AG55*AE55</f>
         <v/>
       </c>
-      <c r="AK55" s="6">
-        <f>VLOOKUP(B55,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK55" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="117" customHeight="1">
@@ -12620,9 +12670,10 @@
         <f>AG56*AE56</f>
         <v/>
       </c>
-      <c r="AK56" s="6">
-        <f>VLOOKUP(B56,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK56" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="117" customHeight="1">
@@ -12701,9 +12752,10 @@
         <f>AG57*AE57</f>
         <v/>
       </c>
-      <c r="AK57" s="6">
-        <f>VLOOKUP(B57,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK57" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="117" customHeight="1">
@@ -12782,9 +12834,10 @@
         <f>AG58*AE58</f>
         <v/>
       </c>
-      <c r="AK58" s="6">
-        <f>VLOOKUP(B58,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK58" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="117" customHeight="1">
@@ -12857,9 +12910,10 @@
         <f>AG59*AE59</f>
         <v/>
       </c>
-      <c r="AK59" s="6">
-        <f>VLOOKUP(B59,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK59" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="117" customHeight="1">
@@ -12936,9 +12990,10 @@
         <f>AG60*AE60</f>
         <v/>
       </c>
-      <c r="AK60" s="6">
-        <f>VLOOKUP(B60,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK60" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="117" customHeight="1">
@@ -13017,9 +13072,10 @@
         <f>AG61*AE61</f>
         <v/>
       </c>
-      <c r="AK61" s="6">
-        <f>VLOOKUP(B61,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK61" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="117" customHeight="1">
@@ -13096,9 +13152,10 @@
         <f>AG62*AE62</f>
         <v/>
       </c>
-      <c r="AK62" s="6">
-        <f>VLOOKUP(B62,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK62" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="117" customHeight="1">
@@ -13177,9 +13234,10 @@
         <f>AG63*AE63</f>
         <v/>
       </c>
-      <c r="AK63" s="6">
-        <f>VLOOKUP(B63,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK63" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="117" customHeight="1">
@@ -13250,9 +13308,10 @@
         <f>AG64*AE64</f>
         <v/>
       </c>
-      <c r="AK64" s="6">
-        <f>VLOOKUP(B64,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK64" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="117" customHeight="1">
@@ -13329,9 +13388,10 @@
         <f>AG65*AE65</f>
         <v/>
       </c>
-      <c r="AK65" s="6">
-        <f>VLOOKUP(B65,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK65" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="117" customHeight="1">
@@ -13404,9 +13464,10 @@
         <f>AG66*AE66</f>
         <v/>
       </c>
-      <c r="AK66" s="6">
-        <f>VLOOKUP(B66,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK66" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="117" customHeight="1">
@@ -13481,9 +13542,10 @@
         <f>AG67*AE67</f>
         <v/>
       </c>
-      <c r="AK67" s="6">
-        <f>VLOOKUP(B67,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK67" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="68" ht="117" customHeight="1">
@@ -13558,9 +13620,10 @@
         <f>AG68*AE68</f>
         <v/>
       </c>
-      <c r="AK68" s="6">
-        <f>VLOOKUP(B68,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK68" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="117" customHeight="1">
@@ -13633,9 +13696,10 @@
         <f>AG69*AE69</f>
         <v/>
       </c>
-      <c r="AK69" s="6">
-        <f>VLOOKUP(B69,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK69" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="117" customHeight="1">
@@ -13710,9 +13774,10 @@
         <f>AG70*AE70</f>
         <v/>
       </c>
-      <c r="AK70" s="6">
-        <f>VLOOKUP(B70,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK70" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="117" customHeight="1">
@@ -13783,9 +13848,10 @@
         <f>AG71*AE71</f>
         <v/>
       </c>
-      <c r="AK71" s="6">
-        <f>VLOOKUP(B71,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK71" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="117" customHeight="1">
@@ -13860,9 +13926,10 @@
         <f>AG72*AE72</f>
         <v/>
       </c>
-      <c r="AK72" s="6">
-        <f>VLOOKUP(B72,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK72" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="117" customHeight="1">
@@ -13941,9 +14008,10 @@
         <f>AG73*AE73</f>
         <v/>
       </c>
-      <c r="AK73" s="6">
-        <f>VLOOKUP(B73,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK73" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="117" customHeight="1">
@@ -14020,9 +14088,10 @@
         <f>AG74*AE74</f>
         <v/>
       </c>
-      <c r="AK74" s="6">
-        <f>VLOOKUP(B74,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK74" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="117" customHeight="1">
@@ -14095,9 +14164,10 @@
         <f>AG75*AE75</f>
         <v/>
       </c>
-      <c r="AK75" s="6">
-        <f>VLOOKUP(B75,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK75" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="117" customHeight="1">
@@ -14174,9 +14244,10 @@
         <f>AG76*AE76</f>
         <v/>
       </c>
-      <c r="AK76" s="6">
-        <f>VLOOKUP(B76,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK76" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="117" customHeight="1">
@@ -14251,9 +14322,10 @@
         <f>AG77*AE77</f>
         <v/>
       </c>
-      <c r="AK77" s="6">
-        <f>VLOOKUP(B77,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK77" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="117" customHeight="1">
@@ -14332,9 +14404,10 @@
         <f>AG78*AE78</f>
         <v/>
       </c>
-      <c r="AK78" s="6">
-        <f>VLOOKUP(B78,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK78" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="117" customHeight="1">
@@ -14409,9 +14482,10 @@
         <f>AG79*AE79</f>
         <v/>
       </c>
-      <c r="AK79" s="6">
-        <f>VLOOKUP(B79,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK79" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="117" customHeight="1">
@@ -14490,9 +14564,10 @@
         <f>AG80*AE80</f>
         <v/>
       </c>
-      <c r="AK80" s="6">
-        <f>VLOOKUP(B80,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK80" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="117" customHeight="1">
@@ -14565,9 +14640,10 @@
         <f>AG81*AE81</f>
         <v/>
       </c>
-      <c r="AK81" s="6">
-        <f>VLOOKUP(B81,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK81" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="117" customHeight="1">
@@ -14640,9 +14716,10 @@
         <f>AG82*AE82</f>
         <v/>
       </c>
-      <c r="AK82" s="6">
-        <f>VLOOKUP(B82,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK82" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="117" customHeight="1">
@@ -14717,9 +14794,10 @@
         <f>AG83*AE83</f>
         <v/>
       </c>
-      <c r="AK83" s="6">
-        <f>VLOOKUP(B83,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK83" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="117" customHeight="1">
@@ -14794,9 +14872,10 @@
         <f>AG84*AE84</f>
         <v/>
       </c>
-      <c r="AK84" s="6">
-        <f>VLOOKUP(B84,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK84" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="117" customHeight="1">
@@ -14873,9 +14952,10 @@
         <f>AG85*AE85</f>
         <v/>
       </c>
-      <c r="AK85" s="6">
-        <f>VLOOKUP(B85,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK85" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="117" customHeight="1">
@@ -14948,9 +15028,10 @@
         <f>AG86*AE86</f>
         <v/>
       </c>
-      <c r="AK86" s="6">
-        <f>VLOOKUP(B86,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK86" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="117" customHeight="1">
@@ -15027,9 +15108,10 @@
         <f>AG87*AE87</f>
         <v/>
       </c>
-      <c r="AK87" s="6">
-        <f>VLOOKUP(B87,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK87" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="117" customHeight="1">
@@ -15106,9 +15188,10 @@
         <f>AG88*AE88</f>
         <v/>
       </c>
-      <c r="AK88" s="6">
-        <f>VLOOKUP(B88,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK88" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="117" customHeight="1">
@@ -15181,9 +15264,10 @@
         <f>AG89*AE89</f>
         <v/>
       </c>
-      <c r="AK89" s="6">
-        <f>VLOOKUP(B89,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK89" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="117" customHeight="1">
@@ -15258,9 +15342,10 @@
         <f>AG90*AE90</f>
         <v/>
       </c>
-      <c r="AK90" s="6">
-        <f>VLOOKUP(B90,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK90" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="117" customHeight="1">
@@ -15331,9 +15416,10 @@
         <f>AG91*AE91</f>
         <v/>
       </c>
-      <c r="AK91" s="6">
-        <f>VLOOKUP(B91,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK91" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="117" customHeight="1">
@@ -15408,9 +15494,10 @@
         <f>AG92*AE92</f>
         <v/>
       </c>
-      <c r="AK92" s="6">
-        <f>VLOOKUP(B92,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK92" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="117" customHeight="1">
@@ -15485,9 +15572,10 @@
         <f>AG93*AE93</f>
         <v/>
       </c>
-      <c r="AK93" s="6">
-        <f>VLOOKUP(B93,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK93" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="117" customHeight="1">
@@ -15564,9 +15652,10 @@
         <f>AG94*AE94</f>
         <v/>
       </c>
-      <c r="AK94" s="6">
-        <f>VLOOKUP(B94,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK94" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="117" customHeight="1">
@@ -15643,9 +15732,10 @@
         <f>AG95*AE95</f>
         <v/>
       </c>
-      <c r="AK95" s="6">
-        <f>VLOOKUP(B95,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK95" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="117" customHeight="1">
@@ -15720,9 +15810,10 @@
         <f>AG96*AE96</f>
         <v/>
       </c>
-      <c r="AK96" s="6">
-        <f>VLOOKUP(B96,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK96" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="117" customHeight="1">
@@ -15795,9 +15886,10 @@
         <f>AG97*AE97</f>
         <v/>
       </c>
-      <c r="AK97" s="6">
-        <f>VLOOKUP(B97,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK97" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="98" ht="117" customHeight="1">
@@ -15874,9 +15966,10 @@
         <f>AG98*AE98</f>
         <v/>
       </c>
-      <c r="AK98" s="6">
-        <f>VLOOKUP(B98,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK98" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="117" customHeight="1">
@@ -15947,9 +16040,10 @@
         <f>AG99*AE99</f>
         <v/>
       </c>
-      <c r="AK99" s="6">
-        <f>VLOOKUP(B99,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK99" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="117" customHeight="1">
@@ -16022,9 +16116,10 @@
         <f>AG100*AE100</f>
         <v/>
       </c>
-      <c r="AK100" s="6">
-        <f>VLOOKUP(B100,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK100" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="117" customHeight="1">
@@ -16095,9 +16190,10 @@
         <f>AG101*AE101</f>
         <v/>
       </c>
-      <c r="AK101" s="6">
-        <f>VLOOKUP(B101,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK101" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="102" ht="117" customHeight="1">
@@ -16174,9 +16270,10 @@
         <f>AG102*AE102</f>
         <v/>
       </c>
-      <c r="AK102" s="6">
-        <f>VLOOKUP(B102,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK102" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="103" ht="117" customHeight="1">
@@ -16249,9 +16346,10 @@
         <f>AG103*AE103</f>
         <v/>
       </c>
-      <c r="AK103" s="6">
-        <f>VLOOKUP(B103,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK103" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="117" customHeight="1">
@@ -16326,9 +16424,10 @@
         <f>AG104*AE104</f>
         <v/>
       </c>
-      <c r="AK104" s="6">
-        <f>VLOOKUP(B104,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK104" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="117" customHeight="1">
@@ -16399,9 +16498,10 @@
         <f>AG105*AE105</f>
         <v/>
       </c>
-      <c r="AK105" s="6">
-        <f>VLOOKUP(B105,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK105" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="106" ht="117" customHeight="1">
@@ -16474,9 +16574,10 @@
         <f>AG106*AE106</f>
         <v/>
       </c>
-      <c r="AK106" s="6">
-        <f>VLOOKUP(B106,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK106" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="107" ht="117" customHeight="1">
@@ -16551,9 +16652,10 @@
         <f>AG107*AE107</f>
         <v/>
       </c>
-      <c r="AK107" s="6">
-        <f>VLOOKUP(B107,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK107" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="108" ht="117" customHeight="1">
@@ -16624,9 +16726,10 @@
         <f>AG108*AE108</f>
         <v/>
       </c>
-      <c r="AK108" s="6">
-        <f>VLOOKUP(B108,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK108" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="109" ht="117" customHeight="1">
@@ -16699,9 +16802,10 @@
         <f>AG109*AE109</f>
         <v/>
       </c>
-      <c r="AK109" s="6">
-        <f>VLOOKUP(B109,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK109" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="110" ht="117" customHeight="1">
@@ -16772,9 +16876,10 @@
         <f>AG110*AE110</f>
         <v/>
       </c>
-      <c r="AK110" s="6">
-        <f>VLOOKUP(B110,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK110" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="117" customHeight="1">
@@ -16849,9 +16954,10 @@
         <f>AG111*AE111</f>
         <v/>
       </c>
-      <c r="AK111" s="6">
-        <f>VLOOKUP(B111,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK111" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="117" customHeight="1">
@@ -16926,9 +17032,10 @@
         <f>AG112*AE112</f>
         <v/>
       </c>
-      <c r="AK112" s="6">
-        <f>VLOOKUP(B112,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK112" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="113" ht="117" customHeight="1">
@@ -17003,9 +17110,10 @@
         <f>AG113*AE113</f>
         <v/>
       </c>
-      <c r="AK113" s="6">
-        <f>VLOOKUP(B113,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK113" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="114" ht="117" customHeight="1">
@@ -17080,9 +17188,10 @@
         <f>AG114*AE114</f>
         <v/>
       </c>
-      <c r="AK114" s="6">
-        <f>VLOOKUP(B114,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK114" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="115" ht="117" customHeight="1">
@@ -17155,9 +17264,10 @@
         <f>AG115*AE115</f>
         <v/>
       </c>
-      <c r="AK115" s="6">
-        <f>VLOOKUP(B115,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK115" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="116" ht="117" customHeight="1">
@@ -17230,9 +17340,10 @@
         <f>AG116*AE116</f>
         <v/>
       </c>
-      <c r="AK116" s="6">
-        <f>VLOOKUP(B116,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK116" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="117" ht="117" customHeight="1">
@@ -17307,9 +17418,10 @@
         <f>AG117*AE117</f>
         <v/>
       </c>
-      <c r="AK117" s="6">
-        <f>VLOOKUP(B117,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK117" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="118" ht="117" customHeight="1">
@@ -17382,9 +17494,10 @@
         <f>AG118*AE118</f>
         <v/>
       </c>
-      <c r="AK118" s="6">
-        <f>VLOOKUP(B118,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK118" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="119" ht="117" customHeight="1">
@@ -17459,9 +17572,10 @@
         <f>AG119*AE119</f>
         <v/>
       </c>
-      <c r="AK119" s="6">
-        <f>VLOOKUP(B119,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK119" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="120" ht="117" customHeight="1">
@@ -17536,9 +17650,10 @@
         <f>AG120*AE120</f>
         <v/>
       </c>
-      <c r="AK120" s="6">
-        <f>VLOOKUP(B120,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK120" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="121" ht="117" customHeight="1">
@@ -17611,9 +17726,10 @@
         <f>AG121*AE121</f>
         <v/>
       </c>
-      <c r="AK121" s="6">
-        <f>VLOOKUP(B121,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK121" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="122" ht="117" customHeight="1">
@@ -17688,9 +17804,10 @@
         <f>AG122*AE122</f>
         <v/>
       </c>
-      <c r="AK122" s="6">
-        <f>VLOOKUP(B122,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK122" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="123" ht="117" customHeight="1">
@@ -17763,9 +17880,10 @@
         <f>AG123*AE123</f>
         <v/>
       </c>
-      <c r="AK123" s="6">
-        <f>VLOOKUP(B123,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK123" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="124" ht="117" customHeight="1">
@@ -17840,9 +17958,10 @@
         <f>AG124*AE124</f>
         <v/>
       </c>
-      <c r="AK124" s="6">
-        <f>VLOOKUP(B124,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK124" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="125" ht="117" customHeight="1">
@@ -17917,9 +18036,10 @@
         <f>AG125*AE125</f>
         <v/>
       </c>
-      <c r="AK125" s="6">
-        <f>VLOOKUP(B125,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK125" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="126" ht="117" customHeight="1">
@@ -17990,9 +18110,10 @@
         <f>AG126*AE126</f>
         <v/>
       </c>
-      <c r="AK126" s="6">
-        <f>VLOOKUP(B126,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK126" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="127" ht="117" customHeight="1">
@@ -18067,9 +18188,10 @@
         <f>AG127*AE127</f>
         <v/>
       </c>
-      <c r="AK127" s="6">
-        <f>VLOOKUP(B127,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK127" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="128" ht="117" customHeight="1">
@@ -18136,9 +18258,10 @@
         <f>AG128*AE128</f>
         <v/>
       </c>
-      <c r="AK128" s="6">
-        <f>VLOOKUP(B128,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK128" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="129" ht="117" customHeight="1">
@@ -18211,9 +18334,10 @@
         <f>AG129*AE129</f>
         <v/>
       </c>
-      <c r="AK129" s="6">
-        <f>VLOOKUP(B129,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK129" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="130" ht="117" customHeight="1">
@@ -18286,9 +18410,10 @@
         <f>AG130*AE130</f>
         <v/>
       </c>
-      <c r="AK130" s="6">
-        <f>VLOOKUP(B130,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK130" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="131" ht="117" customHeight="1">
@@ -18361,9 +18486,10 @@
         <f>AG131*AE131</f>
         <v/>
       </c>
-      <c r="AK131" s="6">
-        <f>VLOOKUP(B131,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK131" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="132" ht="117" customHeight="1">
@@ -18430,9 +18556,10 @@
         <f>AG132*AE132</f>
         <v/>
       </c>
-      <c r="AK132" s="6">
-        <f>VLOOKUP(B132,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK132" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="133" ht="117" customHeight="1">
@@ -18505,9 +18632,10 @@
         <f>AG133*AE133</f>
         <v/>
       </c>
-      <c r="AK133" s="6">
-        <f>VLOOKUP(B133,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK133" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="134" ht="117" customHeight="1">
@@ -18578,9 +18706,10 @@
         <f>AG134*AE134</f>
         <v/>
       </c>
-      <c r="AK134" s="6">
-        <f>VLOOKUP(B134,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK134" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="135" ht="117" customHeight="1">
@@ -18653,9 +18782,10 @@
         <f>AG135*AE135</f>
         <v/>
       </c>
-      <c r="AK135" s="6">
-        <f>VLOOKUP(B135,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK135" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="136" ht="117" customHeight="1">
@@ -18726,9 +18856,10 @@
         <f>AG136*AE136</f>
         <v/>
       </c>
-      <c r="AK136" s="6">
-        <f>VLOOKUP(B136,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK136" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="137" ht="117" customHeight="1">
@@ -18801,9 +18932,10 @@
         <f>AG137*AE137</f>
         <v/>
       </c>
-      <c r="AK137" s="6">
-        <f>VLOOKUP(B137,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK137" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="138" ht="117" customHeight="1">
@@ -18874,9 +19006,10 @@
         <f>AG138*AE138</f>
         <v/>
       </c>
-      <c r="AK138" s="6">
-        <f>VLOOKUP(B138,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK138" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="139" ht="117" customHeight="1">
@@ -18945,9 +19078,10 @@
         <f>AG139*AE139</f>
         <v/>
       </c>
-      <c r="AK139" s="6">
-        <f>VLOOKUP(B139,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK139" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="140" ht="117" customHeight="1">
@@ -19020,9 +19154,10 @@
         <f>AG140*AE140</f>
         <v/>
       </c>
-      <c r="AK140" s="6">
-        <f>VLOOKUP(B140,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK140" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="141" ht="117" customHeight="1">
@@ -19089,9 +19224,10 @@
         <f>AG141*AE141</f>
         <v/>
       </c>
-      <c r="AK141" s="6">
-        <f>VLOOKUP(B141,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK141" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="142" ht="117" customHeight="1">
@@ -19162,9 +19298,10 @@
         <f>AG142*AE142</f>
         <v/>
       </c>
-      <c r="AK142" s="6">
-        <f>VLOOKUP(B142,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK142" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="143" ht="117" customHeight="1">
@@ -19235,9 +19372,10 @@
         <f>AG143*AE143</f>
         <v/>
       </c>
-      <c r="AK143" s="6">
-        <f>VLOOKUP(B143,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK143" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="144" ht="117" customHeight="1">
@@ -19308,9 +19446,10 @@
         <f>AG144*AE144</f>
         <v/>
       </c>
-      <c r="AK144" s="6">
-        <f>VLOOKUP(B144,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK144" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="145" ht="117" customHeight="1">
@@ -19383,9 +19522,10 @@
         <f>AG145*AE145</f>
         <v/>
       </c>
-      <c r="AK145" s="6">
-        <f>VLOOKUP(B145,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK145" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="146" ht="117" customHeight="1">
@@ -19458,9 +19598,10 @@
         <f>AG146*AE146</f>
         <v/>
       </c>
-      <c r="AK146" s="6">
-        <f>VLOOKUP(B146,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK146" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="147" ht="117" customHeight="1">
@@ -19531,9 +19672,10 @@
         <f>AG147*AE147</f>
         <v/>
       </c>
-      <c r="AK147" s="6">
-        <f>VLOOKUP(B147,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK147" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="148" ht="117" customHeight="1">
@@ -19606,9 +19748,10 @@
         <f>AG148*AE148</f>
         <v/>
       </c>
-      <c r="AK148" s="6">
-        <f>VLOOKUP(B148,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK148" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="149" ht="117" customHeight="1">
@@ -19681,9 +19824,10 @@
         <f>AG149*AE149</f>
         <v/>
       </c>
-      <c r="AK149" s="6">
-        <f>VLOOKUP(B149,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK149" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="150" ht="117" customHeight="1">
@@ -19756,9 +19900,10 @@
         <f>AG150*AE150</f>
         <v/>
       </c>
-      <c r="AK150" s="6">
-        <f>VLOOKUP(B150,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK150" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="151" ht="117" customHeight="1">
@@ -19829,9 +19974,10 @@
         <f>AG151*AE151</f>
         <v/>
       </c>
-      <c r="AK151" s="6">
-        <f>VLOOKUP(B151,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK151" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="152" ht="117" customHeight="1">
@@ -19904,9 +20050,10 @@
         <f>AG152*AE152</f>
         <v/>
       </c>
-      <c r="AK152" s="6">
-        <f>VLOOKUP(B152,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK152" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="153" ht="117" customHeight="1">
@@ -19977,9 +20124,10 @@
         <f>AG153*AE153</f>
         <v/>
       </c>
-      <c r="AK153" s="6">
-        <f>VLOOKUP(B153,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK153" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="154" ht="117" customHeight="1">
@@ -20052,9 +20200,10 @@
         <f>AG154*AE154</f>
         <v/>
       </c>
-      <c r="AK154" s="6">
-        <f>VLOOKUP(B154,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK154" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="155" ht="117" customHeight="1">
@@ -20125,9 +20274,10 @@
         <f>AG155*AE155</f>
         <v/>
       </c>
-      <c r="AK155" s="6">
-        <f>VLOOKUP(B155,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK155" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="156" ht="117" customHeight="1">
@@ -20200,9 +20350,10 @@
         <f>AG156*AE156</f>
         <v/>
       </c>
-      <c r="AK156" s="6">
-        <f>VLOOKUP(B156,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK156" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="157" ht="117" customHeight="1">
@@ -20275,9 +20426,10 @@
         <f>AG157*AE157</f>
         <v/>
       </c>
-      <c r="AK157" s="6">
-        <f>VLOOKUP(B157,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK157" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="158" ht="117" customHeight="1">
@@ -20350,9 +20502,10 @@
         <f>AG158*AE158</f>
         <v/>
       </c>
-      <c r="AK158" s="6">
-        <f>VLOOKUP(B158,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK158" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="159" ht="117" customHeight="1">
@@ -20425,9 +20578,10 @@
         <f>AG159*AE159</f>
         <v/>
       </c>
-      <c r="AK159" s="6">
-        <f>VLOOKUP(B159,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK159" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="160" ht="117" customHeight="1">
@@ -20500,9 +20654,10 @@
         <f>AG160*AE160</f>
         <v/>
       </c>
-      <c r="AK160" s="6">
-        <f>VLOOKUP(B160,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK160" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="161" ht="117" customHeight="1">
@@ -20575,9 +20730,10 @@
         <f>AG161*AE161</f>
         <v/>
       </c>
-      <c r="AK161" s="6">
-        <f>VLOOKUP(B161,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK161" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="162" ht="117" customHeight="1">
@@ -20646,9 +20802,10 @@
         <f>AG162*AE162</f>
         <v/>
       </c>
-      <c r="AK162" s="6">
-        <f>VLOOKUP(B162,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK162" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="163" ht="117" customHeight="1">
@@ -20721,9 +20878,10 @@
         <f>AG163*AE163</f>
         <v/>
       </c>
-      <c r="AK163" s="6">
-        <f>VLOOKUP(B163,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK163" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="164" ht="117" customHeight="1">
@@ -20796,9 +20954,10 @@
         <f>AG164*AE164</f>
         <v/>
       </c>
-      <c r="AK164" s="6">
-        <f>VLOOKUP(B164,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK164" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="165" ht="117" customHeight="1">
@@ -20871,9 +21030,10 @@
         <f>AG165*AE165</f>
         <v/>
       </c>
-      <c r="AK165" s="6">
-        <f>VLOOKUP(B165,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK165" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="166" ht="117" customHeight="1">
@@ -20946,9 +21106,10 @@
         <f>AG166*AE166</f>
         <v/>
       </c>
-      <c r="AK166" s="6">
-        <f>VLOOKUP(B166,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK166" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="167" ht="117" customHeight="1">
@@ -21021,9 +21182,10 @@
         <f>AG167*AE167</f>
         <v/>
       </c>
-      <c r="AK167" s="6">
-        <f>VLOOKUP(B167,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK167" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="168" ht="117" customHeight="1">
@@ -21096,9 +21258,10 @@
         <f>AG168*AE168</f>
         <v/>
       </c>
-      <c r="AK168" s="6">
-        <f>VLOOKUP(B168,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK168" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="169" ht="117" customHeight="1">
@@ -21171,9 +21334,10 @@
         <f>AG169*AE169</f>
         <v/>
       </c>
-      <c r="AK169" s="6">
-        <f>VLOOKUP(B169,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK169" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="170" ht="117" customHeight="1">
@@ -21246,9 +21410,10 @@
         <f>AG170*AE170</f>
         <v/>
       </c>
-      <c r="AK170" s="6">
-        <f>VLOOKUP(B170,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK170" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="171" ht="117" customHeight="1">
@@ -21321,9 +21486,10 @@
         <f>AG171*AE171</f>
         <v/>
       </c>
-      <c r="AK171" s="6">
-        <f>VLOOKUP(B171,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK171" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="172" ht="117" customHeight="1">
@@ -21394,9 +21560,10 @@
         <f>AG172*AE172</f>
         <v/>
       </c>
-      <c r="AK172" s="6">
-        <f>VLOOKUP(B172,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK172" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="173" ht="117" customHeight="1">
@@ -21467,9 +21634,10 @@
         <f>AG173*AE173</f>
         <v/>
       </c>
-      <c r="AK173" s="6">
-        <f>VLOOKUP(B173,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK173" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="174" ht="117" customHeight="1">
@@ -21540,9 +21708,10 @@
         <f>AG174*AE174</f>
         <v/>
       </c>
-      <c r="AK174" s="6">
-        <f>VLOOKUP(B174,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK174" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="175" ht="117" customHeight="1">
@@ -21615,9 +21784,10 @@
         <f>AG175*AE175</f>
         <v/>
       </c>
-      <c r="AK175" s="6">
-        <f>VLOOKUP(B175,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK175" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="176" ht="117" customHeight="1">
@@ -21684,9 +21854,10 @@
         <f>AG176*AE176</f>
         <v/>
       </c>
-      <c r="AK176" s="6">
-        <f>VLOOKUP(B176,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK176" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="177" ht="117" customHeight="1">
@@ -21753,9 +21924,10 @@
         <f>AG177*AE177</f>
         <v/>
       </c>
-      <c r="AK177" s="6">
-        <f>VLOOKUP(B177,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK177" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="178" ht="117" customHeight="1">
@@ -21826,9 +21998,10 @@
         <f>AG178*AE178</f>
         <v/>
       </c>
-      <c r="AK178" s="6">
-        <f>VLOOKUP(B178,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK178" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="179" ht="117" customHeight="1">
@@ -21895,9 +22068,10 @@
         <f>AG179*AE179</f>
         <v/>
       </c>
-      <c r="AK179" s="6">
-        <f>VLOOKUP(B179,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK179" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="180" ht="117" customHeight="1">
@@ -21968,9 +22142,10 @@
         <f>AG180*AE180</f>
         <v/>
       </c>
-      <c r="AK180" s="6">
-        <f>VLOOKUP(B180,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK180" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="181" ht="117" customHeight="1">
@@ -22037,9 +22212,10 @@
         <f>AG181*AE181</f>
         <v/>
       </c>
-      <c r="AK181" s="6">
-        <f>VLOOKUP(B181,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK181" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="182" ht="117" customHeight="1">
@@ -22110,9 +22286,10 @@
         <f>AG182*AE182</f>
         <v/>
       </c>
-      <c r="AK182" s="6">
-        <f>VLOOKUP(B182,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK182" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="183" ht="117" customHeight="1">
@@ -22183,9 +22360,10 @@
         <f>AG183*AE183</f>
         <v/>
       </c>
-      <c r="AK183" s="6">
-        <f>VLOOKUP(B183,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK183" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="184" ht="117" customHeight="1">
@@ -22256,9 +22434,10 @@
         <f>AG184*AE184</f>
         <v/>
       </c>
-      <c r="AK184" s="6">
-        <f>VLOOKUP(B184,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK184" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="185" ht="117" customHeight="1">
@@ -22329,9 +22508,10 @@
         <f>AG185*AE185</f>
         <v/>
       </c>
-      <c r="AK185" s="6">
-        <f>VLOOKUP(B185,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK185" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="186" ht="117" customHeight="1">
@@ -22398,9 +22578,10 @@
         <f>AG186*AE186</f>
         <v/>
       </c>
-      <c r="AK186" s="6">
-        <f>VLOOKUP(B186,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK186" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="187" ht="117" customHeight="1">
@@ -22471,9 +22652,10 @@
         <f>AG187*AE187</f>
         <v/>
       </c>
-      <c r="AK187" s="6">
-        <f>VLOOKUP(B187,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK187" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="188" ht="117" customHeight="1">
@@ -22544,9 +22726,10 @@
         <f>AG188*AE188</f>
         <v/>
       </c>
-      <c r="AK188" s="6">
-        <f>VLOOKUP(B188,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK188" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="189" ht="117" customHeight="1">
@@ -22617,9 +22800,10 @@
         <f>AG189*AE189</f>
         <v/>
       </c>
-      <c r="AK189" s="6">
-        <f>VLOOKUP(B189,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK189" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="190" ht="117" customHeight="1">
@@ -22690,9 +22874,10 @@
         <f>AG190*AE190</f>
         <v/>
       </c>
-      <c r="AK190" s="6">
-        <f>VLOOKUP(B190,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK190" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="191" ht="117" customHeight="1">
@@ -22763,9 +22948,10 @@
         <f>AG191*AE191</f>
         <v/>
       </c>
-      <c r="AK191" s="6">
-        <f>VLOOKUP(B191,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK191" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="192" ht="117" customHeight="1">
@@ -22836,9 +23022,10 @@
         <f>AG192*AE192</f>
         <v/>
       </c>
-      <c r="AK192" s="6">
-        <f>VLOOKUP(B192,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK192" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="193" ht="117" customHeight="1">
@@ -22909,9 +23096,10 @@
         <f>AG193*AE193</f>
         <v/>
       </c>
-      <c r="AK193" s="6">
-        <f>VLOOKUP(B193,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK193" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="194" ht="117" customHeight="1">
@@ -22982,9 +23170,10 @@
         <f>AG194*AE194</f>
         <v/>
       </c>
-      <c r="AK194" s="6">
-        <f>VLOOKUP(B194,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK194" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="195" ht="117" customHeight="1">
@@ -23057,9 +23246,10 @@
         <f>AG195*AE195</f>
         <v/>
       </c>
-      <c r="AK195" s="6">
-        <f>VLOOKUP(B195,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK195" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="196" ht="117" customHeight="1">
@@ -23130,9 +23320,10 @@
         <f>AG196*AE196</f>
         <v/>
       </c>
-      <c r="AK196" s="6">
-        <f>VLOOKUP(B196,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK196" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="197" ht="117" customHeight="1">
@@ -23203,9 +23394,10 @@
         <f>AG197*AE197</f>
         <v/>
       </c>
-      <c r="AK197" s="6">
-        <f>VLOOKUP(B197,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK197" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="198" ht="117" customHeight="1">
@@ -23276,9 +23468,10 @@
         <f>AG198*AE198</f>
         <v/>
       </c>
-      <c r="AK198" s="6">
-        <f>VLOOKUP(B198,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK198" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="199" ht="117" customHeight="1">
@@ -23349,9 +23542,10 @@
         <f>AG199*AE199</f>
         <v/>
       </c>
-      <c r="AK199" s="6">
-        <f>VLOOKUP(B199,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK199" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="200" ht="117" customHeight="1">
@@ -23422,9 +23616,10 @@
         <f>AG200*AE200</f>
         <v/>
       </c>
-      <c r="AK200" s="6">
-        <f>VLOOKUP(B200,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK200" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="201" ht="117" customHeight="1">
@@ -23495,9 +23690,10 @@
         <f>AG201*AE201</f>
         <v/>
       </c>
-      <c r="AK201" s="6">
-        <f>VLOOKUP(B201,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK201" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="202" ht="117" customHeight="1">
@@ -23568,9 +23764,10 @@
         <f>AG202*AE202</f>
         <v/>
       </c>
-      <c r="AK202" s="6">
-        <f>VLOOKUP(B202,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK202" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="203" ht="117" customHeight="1">
@@ -23641,9 +23838,10 @@
         <f>AG203*AE203</f>
         <v/>
       </c>
-      <c r="AK203" s="6">
-        <f>VLOOKUP(B203,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK203" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="204" ht="117" customHeight="1">
@@ -23714,9 +23912,10 @@
         <f>AG204*AE204</f>
         <v/>
       </c>
-      <c r="AK204" s="6">
-        <f>VLOOKUP(B204,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK204" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="205" ht="117" customHeight="1">
@@ -23783,9 +23982,10 @@
         <f>AG205*AE205</f>
         <v/>
       </c>
-      <c r="AK205" s="6">
-        <f>VLOOKUP(B205,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK205" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="206" ht="117" customHeight="1">
@@ -23856,9 +24056,10 @@
         <f>AG206*AE206</f>
         <v/>
       </c>
-      <c r="AK206" s="6">
-        <f>VLOOKUP(B206,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK206" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="207" ht="117" customHeight="1">
@@ -23929,9 +24130,10 @@
         <f>AG207*AE207</f>
         <v/>
       </c>
-      <c r="AK207" s="6">
-        <f>VLOOKUP(B207,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK207" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="208" ht="117" customHeight="1">
@@ -24002,9 +24204,10 @@
         <f>AG208*AE208</f>
         <v/>
       </c>
-      <c r="AK208" s="6">
-        <f>VLOOKUP(B208,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK208" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="209" ht="117" customHeight="1">
@@ -24075,9 +24278,10 @@
         <f>AG209*AE209</f>
         <v/>
       </c>
-      <c r="AK209" s="6">
-        <f>VLOOKUP(B209,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK209" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="210" ht="117" customHeight="1">
@@ -24148,9 +24352,10 @@
         <f>AG210*AE210</f>
         <v/>
       </c>
-      <c r="AK210" s="6">
-        <f>VLOOKUP(B210,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK210" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="211" ht="117" customHeight="1">
@@ -24217,9 +24422,10 @@
         <f>AG211*AE211</f>
         <v/>
       </c>
-      <c r="AK211" s="6">
-        <f>VLOOKUP(B211,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK211" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="212" ht="117" customHeight="1">
@@ -24286,9 +24492,10 @@
         <f>AG212*AE212</f>
         <v/>
       </c>
-      <c r="AK212" s="6">
-        <f>VLOOKUP(B212,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK212" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="213" ht="117" customHeight="1">
@@ -24355,9 +24562,10 @@
         <f>AG213*AE213</f>
         <v/>
       </c>
-      <c r="AK213" s="6">
-        <f>VLOOKUP(B213,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK213" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="214" ht="117" customHeight="1">
@@ -24428,9 +24636,10 @@
         <f>AG214*AE214</f>
         <v/>
       </c>
-      <c r="AK214" s="6">
-        <f>VLOOKUP(B214,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK214" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="215" ht="117" customHeight="1">
@@ -24501,9 +24710,10 @@
         <f>AG215*AE215</f>
         <v/>
       </c>
-      <c r="AK215" s="6">
-        <f>VLOOKUP(B215,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK215" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="216" ht="117" customHeight="1">
@@ -24574,9 +24784,10 @@
         <f>AG216*AE216</f>
         <v/>
       </c>
-      <c r="AK216" s="6">
-        <f>VLOOKUP(B216,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK216" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="217" ht="117" customHeight="1">
@@ -24647,9 +24858,10 @@
         <f>AG217*AE217</f>
         <v/>
       </c>
-      <c r="AK217" s="6">
-        <f>VLOOKUP(B217,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK217" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="218" ht="117" customHeight="1">
@@ -24720,9 +24932,10 @@
         <f>AG218*AE218</f>
         <v/>
       </c>
-      <c r="AK218" s="6">
-        <f>VLOOKUP(B218,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK218" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="219" ht="117" customHeight="1">
@@ -24793,9 +25006,10 @@
         <f>AG219*AE219</f>
         <v/>
       </c>
-      <c r="AK219" s="6">
-        <f>VLOOKUP(B219,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK219" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="220" ht="117" customHeight="1">
@@ -24866,9 +25080,10 @@
         <f>AG220*AE220</f>
         <v/>
       </c>
-      <c r="AK220" s="6">
-        <f>VLOOKUP(B220,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK220" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="221" ht="117" customHeight="1">
@@ -24939,9 +25154,10 @@
         <f>AG221*AE221</f>
         <v/>
       </c>
-      <c r="AK221" s="6">
-        <f>VLOOKUP(B221,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK221" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="222" ht="117" customHeight="1">
@@ -25012,9 +25228,10 @@
         <f>AG222*AE222</f>
         <v/>
       </c>
-      <c r="AK222" s="6">
-        <f>VLOOKUP(B222,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK222" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="223" ht="117" customHeight="1">
@@ -25085,9 +25302,10 @@
         <f>AG223*AE223</f>
         <v/>
       </c>
-      <c r="AK223" s="6">
-        <f>VLOOKUP(B223,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK223" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="224" ht="117" customHeight="1">
@@ -25158,9 +25376,10 @@
         <f>AG224*AE224</f>
         <v/>
       </c>
-      <c r="AK224" s="6">
-        <f>VLOOKUP(B224,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK224" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="225" ht="117" customHeight="1">
@@ -25231,9 +25450,10 @@
         <f>AG225*AE225</f>
         <v/>
       </c>
-      <c r="AK225" s="6">
-        <f>VLOOKUP(B225,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK225" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="226" ht="117" customHeight="1">
@@ -25304,9 +25524,10 @@
         <f>AG226*AE226</f>
         <v/>
       </c>
-      <c r="AK226" s="6">
-        <f>VLOOKUP(B226,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK226" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="227" ht="117" customHeight="1">
@@ -25377,9 +25598,10 @@
         <f>AG227*AE227</f>
         <v/>
       </c>
-      <c r="AK227" s="6">
-        <f>VLOOKUP(B227,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK227" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="228" ht="117" customHeight="1">
@@ -25450,9 +25672,10 @@
         <f>AG228*AE228</f>
         <v/>
       </c>
-      <c r="AK228" s="6">
-        <f>VLOOKUP(B228,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK228" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="229" ht="117" customHeight="1">
@@ -25523,9 +25746,10 @@
         <f>AG229*AE229</f>
         <v/>
       </c>
-      <c r="AK229" s="6">
-        <f>VLOOKUP(B229,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK229" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="230" ht="117" customHeight="1">
@@ -25596,9 +25820,10 @@
         <f>AG230*AE230</f>
         <v/>
       </c>
-      <c r="AK230" s="6">
-        <f>VLOOKUP(B230,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK230" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="231" ht="117" customHeight="1">
@@ -25669,9 +25894,10 @@
         <f>AG231*AE231</f>
         <v/>
       </c>
-      <c r="AK231" s="6">
-        <f>VLOOKUP(B231,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK231" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="232" ht="117" customHeight="1">
@@ -25742,9 +25968,10 @@
         <f>AG232*AE232</f>
         <v/>
       </c>
-      <c r="AK232" s="6">
-        <f>VLOOKUP(B232,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK232" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="233" ht="117" customHeight="1">
@@ -25815,9 +26042,10 @@
         <f>AG233*AE233</f>
         <v/>
       </c>
-      <c r="AK233" s="6">
-        <f>VLOOKUP(B233,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK233" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="234" ht="117" customHeight="1">
@@ -25888,9 +26116,10 @@
         <f>AG234*AE234</f>
         <v/>
       </c>
-      <c r="AK234" s="6">
-        <f>VLOOKUP(B234,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK234" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="235" ht="117" customHeight="1">
@@ -25961,9 +26190,10 @@
         <f>AG235*AE235</f>
         <v/>
       </c>
-      <c r="AK235" s="6">
-        <f>VLOOKUP(B235,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK235" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="236" ht="117" customHeight="1">
@@ -26034,9 +26264,10 @@
         <f>AG236*AE236</f>
         <v/>
       </c>
-      <c r="AK236" s="6">
-        <f>VLOOKUP(B236,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK236" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="237" ht="117" customHeight="1">
@@ -26107,9 +26338,10 @@
         <f>AG237*AE237</f>
         <v/>
       </c>
-      <c r="AK237" s="6">
-        <f>VLOOKUP(B237,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK237" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="238" ht="117" customHeight="1">
@@ -26180,9 +26412,10 @@
         <f>AG238*AE238</f>
         <v/>
       </c>
-      <c r="AK238" s="6">
-        <f>VLOOKUP(B238,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK238" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="239" ht="117" customHeight="1">
@@ -26253,9 +26486,10 @@
         <f>AG239*AE239</f>
         <v/>
       </c>
-      <c r="AK239" s="6">
-        <f>VLOOKUP(B239,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK239" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="240" ht="117" customHeight="1">
@@ -26326,9 +26560,10 @@
         <f>AG240*AE240</f>
         <v/>
       </c>
-      <c r="AK240" s="6">
-        <f>VLOOKUP(B240,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK240" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="241" ht="117" customHeight="1">
@@ -26399,9 +26634,10 @@
         <f>AG241*AE241</f>
         <v/>
       </c>
-      <c r="AK241" s="6">
-        <f>VLOOKUP(B241,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK241" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="242" ht="117" customHeight="1">
@@ -26472,9 +26708,10 @@
         <f>AG242*AE242</f>
         <v/>
       </c>
-      <c r="AK242" s="6">
-        <f>VLOOKUP(B242,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK242" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="243" ht="117" customHeight="1">
@@ -26545,9 +26782,10 @@
         <f>AG243*AE243</f>
         <v/>
       </c>
-      <c r="AK243" s="6">
-        <f>VLOOKUP(B243,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK243" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="244" ht="117" customHeight="1">
@@ -26618,9 +26856,10 @@
         <f>AG244*AE244</f>
         <v/>
       </c>
-      <c r="AK244" s="6">
-        <f>VLOOKUP(B244,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK244" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="245" ht="117" customHeight="1">
@@ -26687,9 +26926,10 @@
         <f>AG245*AE245</f>
         <v/>
       </c>
-      <c r="AK245" s="6">
-        <f>VLOOKUP(B245,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK245" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="246" ht="117" customHeight="1">
@@ -26760,9 +27000,10 @@
         <f>AG246*AE246</f>
         <v/>
       </c>
-      <c r="AK246" s="6">
-        <f>VLOOKUP(B246,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK246" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="247" ht="117" customHeight="1">
@@ -26833,9 +27074,10 @@
         <f>AG247*AE247</f>
         <v/>
       </c>
-      <c r="AK247" s="6">
-        <f>VLOOKUP(B247,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK247" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="248" ht="117" customHeight="1">
@@ -26906,9 +27148,10 @@
         <f>AG248*AE248</f>
         <v/>
       </c>
-      <c r="AK248" s="6">
-        <f>VLOOKUP(B248,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK248" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="249" ht="117" customHeight="1">
@@ -26979,9 +27222,10 @@
         <f>AG249*AE249</f>
         <v/>
       </c>
-      <c r="AK249" s="6">
-        <f>VLOOKUP(B249,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK249" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="250" ht="117" customHeight="1">
@@ -27052,9 +27296,10 @@
         <f>AG250*AE250</f>
         <v/>
       </c>
-      <c r="AK250" s="6">
-        <f>VLOOKUP(B250,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK250" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="251" ht="117" customHeight="1">
@@ -27125,9 +27370,10 @@
         <f>AG251*AE251</f>
         <v/>
       </c>
-      <c r="AK251" s="6">
-        <f>VLOOKUP(B251,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK251" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="252" ht="117" customHeight="1">
@@ -27198,9 +27444,10 @@
         <f>AG252*AE252</f>
         <v/>
       </c>
-      <c r="AK252" s="6">
-        <f>VLOOKUP(B252,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK252" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="253" ht="117" customHeight="1">
@@ -27271,9 +27518,10 @@
         <f>AG253*AE253</f>
         <v/>
       </c>
-      <c r="AK253" s="6">
-        <f>VLOOKUP(B253,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK253" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="254" ht="117" customHeight="1">
@@ -27340,9 +27588,10 @@
         <f>AG254*AE254</f>
         <v/>
       </c>
-      <c r="AK254" s="6">
-        <f>VLOOKUP(B254,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK254" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="255" ht="117" customHeight="1">
@@ -27413,9 +27662,10 @@
         <f>AG255*AE255</f>
         <v/>
       </c>
-      <c r="AK255" s="6">
-        <f>VLOOKUP(B255,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK255" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="256" ht="117" customHeight="1">
@@ -27486,9 +27736,10 @@
         <f>AG256*AE256</f>
         <v/>
       </c>
-      <c r="AK256" s="6">
-        <f>VLOOKUP(B256,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK256" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="257" ht="117" customHeight="1">
@@ -27559,9 +27810,10 @@
         <f>AG257*AE257</f>
         <v/>
       </c>
-      <c r="AK257" s="6">
-        <f>VLOOKUP(B257,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK257" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="258" ht="117" customHeight="1">
@@ -27632,9 +27884,10 @@
         <f>AG258*AE258</f>
         <v/>
       </c>
-      <c r="AK258" s="6">
-        <f>VLOOKUP(B258,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK258" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="259" ht="117" customHeight="1">
@@ -27705,9 +27958,10 @@
         <f>AG259*AE259</f>
         <v/>
       </c>
-      <c r="AK259" s="6">
-        <f>VLOOKUP(B259,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK259" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="260" ht="117" customHeight="1">
@@ -27778,9 +28032,10 @@
         <f>AG260*AE260</f>
         <v/>
       </c>
-      <c r="AK260" s="6">
-        <f>VLOOKUP(B260,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK260" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="261" ht="117" customHeight="1">
@@ -27851,9 +28106,10 @@
         <f>AG261*AE261</f>
         <v/>
       </c>
-      <c r="AK261" s="6">
-        <f>VLOOKUP(B261,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK261" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="262" ht="117" customHeight="1">
@@ -27924,9 +28180,10 @@
         <f>AG262*AE262</f>
         <v/>
       </c>
-      <c r="AK262" s="6">
-        <f>VLOOKUP(B262,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK262" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="263" ht="117" customHeight="1">
@@ -27997,9 +28254,10 @@
         <f>AG263*AE263</f>
         <v/>
       </c>
-      <c r="AK263" s="6">
-        <f>VLOOKUP(B263,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK263" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="264" ht="117" customHeight="1">
@@ -28070,9 +28328,10 @@
         <f>AG264*AE264</f>
         <v/>
       </c>
-      <c r="AK264" s="6">
-        <f>VLOOKUP(B264,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK264" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="265" ht="117" customHeight="1">
@@ -28143,9 +28402,10 @@
         <f>AG265*AE265</f>
         <v/>
       </c>
-      <c r="AK265" s="6">
-        <f>VLOOKUP(B265,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK265" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="266" ht="117" customHeight="1">
@@ -28216,9 +28476,10 @@
         <f>AG266*AE266</f>
         <v/>
       </c>
-      <c r="AK266" s="6">
-        <f>VLOOKUP(B266,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK266" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="267" ht="117" customHeight="1">
@@ -28289,9 +28550,10 @@
         <f>AG267*AE267</f>
         <v/>
       </c>
-      <c r="AK267" s="6">
-        <f>VLOOKUP(B267,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK267" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="268" ht="117" customHeight="1">
@@ -28362,9 +28624,10 @@
         <f>AG268*AE268</f>
         <v/>
       </c>
-      <c r="AK268" s="6">
-        <f>VLOOKUP(B268,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK268" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="269" ht="117" customHeight="1">
@@ -28435,9 +28698,10 @@
         <f>AG269*AE269</f>
         <v/>
       </c>
-      <c r="AK269" s="6">
-        <f>VLOOKUP(B269,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK269" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="270" ht="117" customHeight="1">
@@ -28508,9 +28772,10 @@
         <f>AG270*AE270</f>
         <v/>
       </c>
-      <c r="AK270" s="6">
-        <f>VLOOKUP(B270,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK270" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="271" ht="117" customHeight="1">
@@ -28581,9 +28846,10 @@
         <f>AG271*AE271</f>
         <v/>
       </c>
-      <c r="AK271" s="6">
-        <f>VLOOKUP(B271,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK271" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="272" ht="117" customHeight="1">
@@ -28654,9 +28920,10 @@
         <f>AG272*AE272</f>
         <v/>
       </c>
-      <c r="AK272" s="6">
-        <f>VLOOKUP(B272,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK272" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="273" ht="117" customHeight="1">
@@ -28723,9 +28990,10 @@
         <f>AG273*AE273</f>
         <v/>
       </c>
-      <c r="AK273" s="6">
-        <f>VLOOKUP(B273,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK273" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="274" ht="117" customHeight="1">
@@ -28796,9 +29064,10 @@
         <f>AG274*AE274</f>
         <v/>
       </c>
-      <c r="AK274" s="6">
-        <f>VLOOKUP(B274,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK274" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="275" ht="117" customHeight="1">
@@ -28869,9 +29138,10 @@
         <f>AG275*AE275</f>
         <v/>
       </c>
-      <c r="AK275" s="6">
-        <f>VLOOKUP(B275,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK275" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="276" ht="117" customHeight="1">
@@ -28942,9 +29212,10 @@
         <f>AG276*AE276</f>
         <v/>
       </c>
-      <c r="AK276" s="6">
-        <f>VLOOKUP(B276,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK276" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="277" ht="117" customHeight="1">
@@ -29015,9 +29286,10 @@
         <f>AG277*AE277</f>
         <v/>
       </c>
-      <c r="AK277" s="6">
-        <f>VLOOKUP(B277,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK277" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="278" ht="117" customHeight="1">
@@ -29088,9 +29360,10 @@
         <f>AG278*AE278</f>
         <v/>
       </c>
-      <c r="AK278" s="6">
-        <f>VLOOKUP(B278,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK278" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="279" ht="117" customHeight="1">
@@ -29161,9 +29434,10 @@
         <f>AG279*AE279</f>
         <v/>
       </c>
-      <c r="AK279" s="6">
-        <f>VLOOKUP(B279,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK279" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="280" ht="117" customHeight="1">
@@ -29234,9 +29508,10 @@
         <f>AG280*AE280</f>
         <v/>
       </c>
-      <c r="AK280" s="6">
-        <f>VLOOKUP(B280,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK280" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="281" ht="117" customHeight="1">
@@ -29307,9 +29582,10 @@
         <f>AG281*AE281</f>
         <v/>
       </c>
-      <c r="AK281" s="6">
-        <f>VLOOKUP(B281,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK281" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="282" ht="117" customHeight="1">
@@ -29380,9 +29656,10 @@
         <f>AG282*AE282</f>
         <v/>
       </c>
-      <c r="AK282" s="6">
-        <f>VLOOKUP(B282,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK282" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="283" ht="117" customHeight="1">
@@ -29453,9 +29730,10 @@
         <f>AG283*AE283</f>
         <v/>
       </c>
-      <c r="AK283" s="6">
-        <f>VLOOKUP(B283,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK283" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="284" ht="117" customHeight="1">
@@ -29522,9 +29800,10 @@
         <f>AG284*AE284</f>
         <v/>
       </c>
-      <c r="AK284" s="6">
-        <f>VLOOKUP(B284,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK284" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="285" ht="117" customHeight="1">
@@ -29595,9 +29874,10 @@
         <f>AG285*AE285</f>
         <v/>
       </c>
-      <c r="AK285" s="6">
-        <f>VLOOKUP(B285,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK285" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="286" ht="117" customHeight="1">
@@ -29668,9 +29948,10 @@
         <f>AG286*AE286</f>
         <v/>
       </c>
-      <c r="AK286" s="6">
-        <f>VLOOKUP(B286,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK286" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="287" ht="117" customHeight="1">
@@ -29741,9 +30022,10 @@
         <f>AG287*AE287</f>
         <v/>
       </c>
-      <c r="AK287" s="6">
-        <f>VLOOKUP(B287,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK287" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="288" ht="117" customHeight="1">
@@ -29814,9 +30096,10 @@
         <f>AG288*AE288</f>
         <v/>
       </c>
-      <c r="AK288" s="6">
-        <f>VLOOKUP(B288,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK288" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="289" ht="117" customHeight="1">
@@ -29887,9 +30170,10 @@
         <f>AG289*AE289</f>
         <v/>
       </c>
-      <c r="AK289" s="6">
-        <f>VLOOKUP(B289,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK289" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="290" ht="117" customHeight="1">
@@ -29960,9 +30244,10 @@
         <f>AG290*AE290</f>
         <v/>
       </c>
-      <c r="AK290" s="6">
-        <f>VLOOKUP(B290,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK290" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="291" ht="117" customHeight="1">
@@ -30029,9 +30314,10 @@
         <f>AG291*AE291</f>
         <v/>
       </c>
-      <c r="AK291" s="6">
-        <f>VLOOKUP(B291,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK291" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="292" ht="117" customHeight="1">
@@ -30102,9 +30388,10 @@
         <f>AG292*AE292</f>
         <v/>
       </c>
-      <c r="AK292" s="6">
-        <f>VLOOKUP(B292,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK292" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="293" ht="117" customHeight="1">
@@ -30175,9 +30462,10 @@
         <f>AG293*AE293</f>
         <v/>
       </c>
-      <c r="AK293" s="6">
-        <f>VLOOKUP(B293,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK293" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="294" ht="117" customHeight="1">
@@ -30248,9 +30536,10 @@
         <f>AG294*AE294</f>
         <v/>
       </c>
-      <c r="AK294" s="6">
-        <f>VLOOKUP(B294,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK294" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="295" ht="117" customHeight="1">
@@ -30321,9 +30610,10 @@
         <f>AG295*AE295</f>
         <v/>
       </c>
-      <c r="AK295" s="6">
-        <f>VLOOKUP(B295,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK295" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="296" ht="117" customHeight="1">
@@ -30394,9 +30684,10 @@
         <f>AG296*AE296</f>
         <v/>
       </c>
-      <c r="AK296" s="6">
-        <f>VLOOKUP(B296,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK296" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="297" ht="117" customHeight="1">
@@ -30467,9 +30758,10 @@
         <f>AG297*AE297</f>
         <v/>
       </c>
-      <c r="AK297" s="6">
-        <f>VLOOKUP(B297,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK297" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="298" ht="117" customHeight="1">
@@ -30540,9 +30832,10 @@
         <f>AG298*AE298</f>
         <v/>
       </c>
-      <c r="AK298" s="6">
-        <f>VLOOKUP(B298,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK298" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="299" ht="117" customHeight="1">
@@ -30613,9 +30906,10 @@
         <f>AG299*AE299</f>
         <v/>
       </c>
-      <c r="AK299" s="6">
-        <f>VLOOKUP(B299,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK299" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="300" ht="117" customHeight="1">
@@ -30686,9 +30980,10 @@
         <f>AG300*AE300</f>
         <v/>
       </c>
-      <c r="AK300" s="6">
-        <f>VLOOKUP(B300,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK300" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="301" ht="117" customHeight="1">
@@ -30759,9 +31054,10 @@
         <f>AG301*AE301</f>
         <v/>
       </c>
-      <c r="AK301" s="6">
-        <f>VLOOKUP(B301,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK301" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="302" ht="117" customHeight="1">
@@ -30832,9 +31128,10 @@
         <f>AG302*AE302</f>
         <v/>
       </c>
-      <c r="AK302" s="6">
-        <f>VLOOKUP(B302,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK302" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="303" ht="117" customHeight="1">
@@ -30901,9 +31198,10 @@
         <f>AG303*AE303</f>
         <v/>
       </c>
-      <c r="AK303" s="6">
-        <f>VLOOKUP(B303,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK303" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="304" ht="117" customHeight="1">
@@ -30974,9 +31272,10 @@
         <f>AG304*AE304</f>
         <v/>
       </c>
-      <c r="AK304" s="6">
-        <f>VLOOKUP(B304,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK304" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="305" ht="117" customHeight="1">
@@ -31047,9 +31346,10 @@
         <f>AG305*AE305</f>
         <v/>
       </c>
-      <c r="AK305" s="6">
-        <f>VLOOKUP(B305,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK305" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="306" ht="117" customHeight="1">
@@ -31120,9 +31420,10 @@
         <f>AG306*AE306</f>
         <v/>
       </c>
-      <c r="AK306" s="6">
-        <f>VLOOKUP(B306,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK306" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="307" ht="117" customHeight="1">
@@ -31195,9 +31496,10 @@
         <f>AG307*AE307</f>
         <v/>
       </c>
-      <c r="AK307" s="6">
-        <f>VLOOKUP(B307,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK307" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="308" ht="117" customHeight="1">
@@ -31264,9 +31566,10 @@
         <f>AG308*AE308</f>
         <v/>
       </c>
-      <c r="AK308" s="6">
-        <f>VLOOKUP(B308,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK308" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="309" ht="117" customHeight="1">
@@ -31333,9 +31636,10 @@
         <f>AG309*AE309</f>
         <v/>
       </c>
-      <c r="AK309" s="6">
-        <f>VLOOKUP(B309,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK309" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="310" ht="117" customHeight="1">
@@ -31402,9 +31706,10 @@
         <f>AG310*AE310</f>
         <v/>
       </c>
-      <c r="AK310" s="6">
-        <f>VLOOKUP(B310,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK310" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="311" ht="117" customHeight="1">
@@ -31475,9 +31780,10 @@
         <f>AG311*AE311</f>
         <v/>
       </c>
-      <c r="AK311" s="6">
-        <f>VLOOKUP(B311,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK311" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="312" ht="117" customHeight="1">
@@ -31548,9 +31854,10 @@
         <f>AG312*AE312</f>
         <v/>
       </c>
-      <c r="AK312" s="6">
-        <f>VLOOKUP(B312,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK312" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="313" ht="117" customHeight="1">
@@ -31621,9 +31928,10 @@
         <f>AG313*AE313</f>
         <v/>
       </c>
-      <c r="AK313" s="6">
-        <f>VLOOKUP(B313,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK313" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="314" ht="117" customHeight="1">
@@ -31694,9 +32002,10 @@
         <f>AG314*AE314</f>
         <v/>
       </c>
-      <c r="AK314" s="6">
-        <f>VLOOKUP(B314,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK314" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="315" ht="117" customHeight="1">
@@ -31763,9 +32072,10 @@
         <f>AG315*AE315</f>
         <v/>
       </c>
-      <c r="AK315" s="6">
-        <f>VLOOKUP(B315,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK315" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="316" ht="117" customHeight="1">
@@ -31836,9 +32146,10 @@
         <f>AG316*AE316</f>
         <v/>
       </c>
-      <c r="AK316" s="6">
-        <f>VLOOKUP(B316,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK316" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="317" ht="117" customHeight="1">
@@ -31909,9 +32220,10 @@
         <f>AG317*AE317</f>
         <v/>
       </c>
-      <c r="AK317" s="6">
-        <f>VLOOKUP(B317,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK317" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="318" ht="117" customHeight="1">
@@ -31982,9 +32294,10 @@
         <f>AG318*AE318</f>
         <v/>
       </c>
-      <c r="AK318" s="6">
-        <f>VLOOKUP(B318,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK318" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="319" ht="117" customHeight="1">
@@ -32055,9 +32368,10 @@
         <f>AG319*AE319</f>
         <v/>
       </c>
-      <c r="AK319" s="6">
-        <f>VLOOKUP(B319,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK319" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="320" ht="117" customHeight="1">
@@ -32124,9 +32438,10 @@
         <f>AG320*AE320</f>
         <v/>
       </c>
-      <c r="AK320" s="6">
-        <f>VLOOKUP(B320,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK320" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="321" ht="117" customHeight="1">
@@ -32193,9 +32508,10 @@
         <f>AG321*AE321</f>
         <v/>
       </c>
-      <c r="AK321" s="6">
-        <f>VLOOKUP(B321,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK321" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="322" ht="117" customHeight="1">
@@ -32266,9 +32582,10 @@
         <f>AG322*AE322</f>
         <v/>
       </c>
-      <c r="AK322" s="6">
-        <f>VLOOKUP(B322,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK322" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="323" ht="117" customHeight="1">
@@ -32339,9 +32656,10 @@
         <f>AG323*AE323</f>
         <v/>
       </c>
-      <c r="AK323" s="6">
-        <f>VLOOKUP(B323,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK323" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="324" ht="117" customHeight="1">
@@ -32412,9 +32730,10 @@
         <f>AG324*AE324</f>
         <v/>
       </c>
-      <c r="AK324" s="6">
-        <f>VLOOKUP(B324,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK324" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="325" ht="117" customHeight="1">
@@ -32485,9 +32804,10 @@
         <f>AG325*AE325</f>
         <v/>
       </c>
-      <c r="AK325" s="6">
-        <f>VLOOKUP(B325,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK325" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="326" ht="117" customHeight="1">
@@ -32558,9 +32878,10 @@
         <f>AG326*AE326</f>
         <v/>
       </c>
-      <c r="AK326" s="6">
-        <f>VLOOKUP(B326,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK326" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="327" ht="117" customHeight="1">
@@ -32631,9 +32952,10 @@
         <f>AG327*AE327</f>
         <v/>
       </c>
-      <c r="AK327" s="6">
-        <f>VLOOKUP(B327,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK327" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="328" ht="117" customHeight="1">
@@ -32704,9 +33026,10 @@
         <f>AG328*AE328</f>
         <v/>
       </c>
-      <c r="AK328" s="6">
-        <f>VLOOKUP(B328,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK328" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="329" ht="117" customHeight="1">
@@ -32777,9 +33100,10 @@
         <f>AG329*AE329</f>
         <v/>
       </c>
-      <c r="AK329" s="6">
-        <f>VLOOKUP(B329,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK329" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="330" ht="117" customHeight="1">
@@ -32850,9 +33174,10 @@
         <f>AG330*AE330</f>
         <v/>
       </c>
-      <c r="AK330" s="6">
-        <f>VLOOKUP(B330,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK330" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="331" ht="117" customHeight="1">
@@ -32923,9 +33248,10 @@
         <f>AG331*AE331</f>
         <v/>
       </c>
-      <c r="AK331" s="6">
-        <f>VLOOKUP(B331,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK331" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="332" ht="117" customHeight="1">
@@ -32996,9 +33322,10 @@
         <f>AG332*AE332</f>
         <v/>
       </c>
-      <c r="AK332" s="6">
-        <f>VLOOKUP(B332,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK332" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="333" ht="117" customHeight="1">
@@ -33069,9 +33396,10 @@
         <f>AG333*AE333</f>
         <v/>
       </c>
-      <c r="AK333" s="6">
-        <f>VLOOKUP(B333,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK333" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="334" ht="117" customHeight="1">
@@ -33142,9 +33470,10 @@
         <f>AG334*AE334</f>
         <v/>
       </c>
-      <c r="AK334" s="6">
-        <f>VLOOKUP(B334,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK334" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="335" ht="117" customHeight="1">
@@ -33215,9 +33544,10 @@
         <f>AG335*AE335</f>
         <v/>
       </c>
-      <c r="AK335" s="6">
-        <f>VLOOKUP(B335,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK335" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
     <row r="336" ht="117" customHeight="1">
@@ -33288,13 +33618,14 @@
         <f>AG336*AE336</f>
         <v/>
       </c>
-      <c r="AK336" s="6">
-        <f>VLOOKUP(B336,[1]RTW!$B:$AD,29,FALSE)</f>
-        <v/>
+      <c r="AK336" s="6" t="inlineStr">
+        <is>
+          <t>#REF</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>